--- a/data/interim/itu_internet_users_pct_processed.xlsx
+++ b/data/interim/itu_internet_users_pct_processed.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,41 +413,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G485"/>
+  <dimension ref="A1:G496"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>country</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>internet_users_pct</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>internet_users_pct</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
         <is>
           <t>series_code</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>series_units</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>data_source</t>
         </is>
@@ -607,7 +595,7 @@
         <v>2014</v>
       </c>
       <c r="C6" t="n">
-        <v>54.6228</v>
+        <v>54.6228058583362</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -640,7 +628,7 @@
         <v>2015</v>
       </c>
       <c r="C7" t="n">
-        <v>59.1008</v>
+        <v>59.1008337674937</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -673,7 +661,7 @@
         <v>2016</v>
       </c>
       <c r="C8" t="n">
-        <v>64.346</v>
+        <v>64.3460297653742</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -706,7 +694,7 @@
         <v>2017</v>
       </c>
       <c r="C9" t="n">
-        <v>64.7449</v>
+        <v>64.7448843250726</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -739,7 +727,7 @@
         <v>2018</v>
       </c>
       <c r="C10" t="n">
-        <v>68.24509999999999</v>
+        <v>68.2450522610271</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -772,7 +760,7 @@
         <v>2019</v>
       </c>
       <c r="C11" t="n">
-        <v>66.54389999999999</v>
+        <v>66.5439496866159</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -805,7 +793,7 @@
         <v>2020</v>
       </c>
       <c r="C12" t="n">
-        <v>76.5077</v>
+        <v>76.50770055</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -838,7 +826,7 @@
         <v>2021</v>
       </c>
       <c r="C13" t="n">
-        <v>78.6123</v>
+        <v>78.61225758</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -871,7 +859,7 @@
         <v>2022</v>
       </c>
       <c r="C14" t="n">
-        <v>77.0277</v>
+        <v>77.02767464999999</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -904,7 +892,7 @@
         <v>2023</v>
       </c>
       <c r="C15" t="n">
-        <v>79.9966</v>
+        <v>79.99663036</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -930,14 +918,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AUT</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2010</v>
+        <v>2024</v>
       </c>
       <c r="C16" t="n">
-        <v>75.17</v>
+        <v>81.33930205999999</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -967,10 +955,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="C17" t="n">
-        <v>78.73999999999999</v>
+        <v>75.17</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1000,10 +988,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="C18" t="n">
-        <v>80.03</v>
+        <v>78.7399930986888</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1033,10 +1021,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="C19" t="n">
-        <v>80.61879999999999</v>
+        <v>80.02999391699031</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1066,10 +1054,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="C20" t="n">
-        <v>80.9958</v>
+        <v>80.61879999999999</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1099,10 +1087,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="C21" t="n">
-        <v>83.9401</v>
+        <v>80.9958249574764</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1132,10 +1120,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="C22" t="n">
-        <v>84.3237</v>
+        <v>83.94014193150259</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1165,10 +1153,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="C23" t="n">
-        <v>87.93559999999999</v>
+        <v>84.3237425711653</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1198,10 +1186,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="C24" t="n">
-        <v>87.4791</v>
+        <v>87.9355865856062</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1231,10 +1219,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C25" t="n">
-        <v>87.7522</v>
+        <v>87.4791372262556</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1264,10 +1252,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C26" t="n">
-        <v>87.5294</v>
+        <v>87.7522047870069</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1297,10 +1285,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C27" t="n">
-        <v>92.5292</v>
+        <v>87.52942813</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1330,10 +1318,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C28" t="n">
-        <v>93.61409999999999</v>
+        <v>92.52915104</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1363,10 +1351,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C29" t="n">
-        <v>95.3347</v>
+        <v>93.61409139</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1396,10 +1384,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C30" t="n">
-        <v>94.91970000000001</v>
+        <v>95.33467116999999</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1425,14 +1413,14 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AZE</t>
+          <t>AUT</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2010</v>
+        <v>2024</v>
       </c>
       <c r="C31" t="n">
-        <v>46</v>
+        <v>94.91974877</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1462,10 +1450,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="C32" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1495,10 +1483,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="C33" t="n">
-        <v>54.2</v>
+        <v>50</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1528,10 +1516,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="C34" t="n">
-        <v>73</v>
+        <v>54.20000076</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1561,10 +1549,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="C35" t="n">
-        <v>75</v>
+        <v>73.000001372</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1594,10 +1582,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="C36" t="n">
-        <v>77</v>
+        <v>75.0000156363396</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1627,10 +1615,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="C37" t="n">
-        <v>78.2</v>
+        <v>77</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1660,10 +1648,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="C38" t="n">
-        <v>79</v>
+        <v>78.2</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1693,10 +1681,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="C39" t="n">
-        <v>79.8</v>
+        <v>79</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1726,10 +1714,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C40" t="n">
-        <v>81.09999999999999</v>
+        <v>79.79999548878961</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1759,10 +1747,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C41" t="n">
-        <v>84.59999999999999</v>
+        <v>81.09999906515471</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1792,10 +1780,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C42" t="n">
-        <v>86</v>
+        <v>84.59999573</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1825,10 +1813,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C43" t="n">
-        <v>88</v>
+        <v>85.99998954</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1858,10 +1846,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C44" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1887,14 +1875,14 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>AZE</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2010</v>
+        <v>2023</v>
       </c>
       <c r="C45" t="n">
-        <v>77.63979999999999</v>
+        <v>89</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1920,14 +1908,14 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>AZE</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2011</v>
+        <v>2024</v>
       </c>
       <c r="C46" t="n">
-        <v>81.61</v>
+        <v>90.43979645</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1957,10 +1945,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C47" t="n">
-        <v>80.72</v>
+        <v>77.6397855126946</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1990,10 +1978,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="C48" t="n">
-        <v>82.17019999999999</v>
+        <v>81.6099959955952</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2023,10 +2011,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C49" t="n">
-        <v>85.0012</v>
+        <v>80.71999054820419</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2056,10 +2044,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="C50" t="n">
-        <v>85.05289999999999</v>
+        <v>82.17019999999999</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2089,10 +2077,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C51" t="n">
-        <v>86.51649999999999</v>
+        <v>85.0012379539925</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -2122,10 +2110,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="C52" t="n">
-        <v>87.6797</v>
+        <v>85.0529417508701</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -2155,10 +2143,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C53" t="n">
-        <v>88.6473</v>
+        <v>86.5164766644457</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -2188,10 +2176,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="C54" t="n">
-        <v>90.2754</v>
+        <v>87.6796808175598</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -2221,10 +2209,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C55" t="n">
-        <v>91.5264</v>
+        <v>88.6473429951691</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2254,10 +2242,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C56" t="n">
-        <v>92.78870000000001</v>
+        <v>90.27542801214101</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2287,10 +2275,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C57" t="n">
-        <v>94.0078</v>
+        <v>91.52641629</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -2320,10 +2308,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="C58" t="n">
-        <v>94.6263</v>
+        <v>92.78867618</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -2353,10 +2341,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="C59" t="n">
-        <v>95.7758</v>
+        <v>94.00783070999999</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -2382,14 +2370,14 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BLR</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2010</v>
+        <v>2023</v>
       </c>
       <c r="C60" t="n">
-        <v>31.8</v>
+        <v>94.62625074</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -2415,14 +2403,14 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BLR</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2011</v>
+        <v>2024</v>
       </c>
       <c r="C61" t="n">
-        <v>39.6489</v>
+        <v>95.77579144000001</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -2452,10 +2440,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C62" t="n">
-        <v>46.91</v>
+        <v>31.8</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -2485,10 +2473,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="C63" t="n">
-        <v>54.17</v>
+        <v>39.6488956598961</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -2518,10 +2506,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C64" t="n">
-        <v>59.0163</v>
+        <v>46.91</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -2551,10 +2539,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="C65" t="n">
-        <v>62.2304</v>
+        <v>54.17</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -2584,10 +2572,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C66" t="n">
-        <v>71.113</v>
+        <v>59.0163187101542</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -2617,10 +2605,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="C67" t="n">
-        <v>74.43640000000001</v>
+        <v>62.230360906803</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -2650,10 +2638,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C68" t="n">
-        <v>79.12990000000001</v>
+        <v>71.1130457603832</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -2683,10 +2671,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="C69" t="n">
-        <v>82.78919999999999</v>
+        <v>74.43644541360359</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -2716,10 +2704,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C70" t="n">
-        <v>85.0879</v>
+        <v>79.12988669193069</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -2749,10 +2737,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C71" t="n">
-        <v>86.8884</v>
+        <v>82.7891520910901</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -2782,10 +2770,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C72" t="n">
-        <v>89.5073</v>
+        <v>85.08791245</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -2815,10 +2803,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="C73" t="n">
-        <v>91.5125</v>
+        <v>86.88841196</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -2848,10 +2836,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="C74" t="n">
-        <v>94.26179999999999</v>
+        <v>89.50733148</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -2877,14 +2865,14 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BGR</t>
+          <t>BLR</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2010</v>
+        <v>2023</v>
       </c>
       <c r="C75" t="n">
-        <v>46.23</v>
+        <v>91.51249979000001</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -2910,14 +2898,14 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BGR</t>
+          <t>BLR</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2011</v>
+        <v>2024</v>
       </c>
       <c r="C76" t="n">
-        <v>47.98</v>
+        <v>94.26182128000001</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -2947,10 +2935,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C77" t="n">
-        <v>51.9</v>
+        <v>46.23</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -2980,10 +2968,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="C78" t="n">
-        <v>53.0615</v>
+        <v>47.9799930506026</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -3013,10 +3001,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C79" t="n">
-        <v>55.4904</v>
+        <v>51.8999876658503</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -3046,10 +3034,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="C80" t="n">
-        <v>56.6563</v>
+        <v>53.0615</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -3079,10 +3067,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C81" t="n">
-        <v>59.8255</v>
+        <v>55.4903766299262</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -3112,10 +3100,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="C82" t="n">
-        <v>63.4101</v>
+        <v>56.6562516053086</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -3145,10 +3133,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C83" t="n">
-        <v>64.782</v>
+        <v>59.825547661014</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -3178,10 +3166,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="C84" t="n">
-        <v>67.947</v>
+        <v>63.4101013837926</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -3211,10 +3199,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C85" t="n">
-        <v>70.16249999999999</v>
+        <v>64.78201069118001</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -3244,10 +3232,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C86" t="n">
-        <v>75.2714</v>
+        <v>67.9469809417603</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -3277,10 +3265,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C87" t="n">
-        <v>79.12690000000001</v>
+        <v>70.16248358999999</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -3310,10 +3298,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="C88" t="n">
-        <v>80.3896</v>
+        <v>75.27144583</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -3343,10 +3331,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="C89" t="n">
-        <v>82.43899999999999</v>
+        <v>79.12686325999999</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -3372,14 +3360,14 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CYP</t>
+          <t>BGR</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>2010</v>
+        <v>2023</v>
       </c>
       <c r="C90" t="n">
-        <v>52.99</v>
+        <v>80.38956462</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -3405,14 +3393,14 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CYP</t>
+          <t>BGR</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>2011</v>
+        <v>2024</v>
       </c>
       <c r="C91" t="n">
-        <v>56.8599</v>
+        <v>82.43895500000001</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -3442,10 +3430,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C92" t="n">
-        <v>60.6899</v>
+        <v>52.99</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -3475,10 +3463,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="C93" t="n">
-        <v>65.45480000000001</v>
+        <v>56.8598923503507</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -3508,10 +3496,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C94" t="n">
-        <v>69.3287</v>
+        <v>60.6898684001903</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -3541,10 +3529,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="C95" t="n">
-        <v>71.7157</v>
+        <v>65.45480000000001</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -3574,10 +3562,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C96" t="n">
-        <v>75.9002</v>
+        <v>69.3286967086473</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -3607,10 +3595,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="C97" t="n">
-        <v>80.7432</v>
+        <v>71.7157409175171</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -3640,10 +3628,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C98" t="n">
-        <v>84.4336</v>
+        <v>75.90020540301251</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -3673,10 +3661,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="C99" t="n">
-        <v>86.06359999999999</v>
+        <v>80.743188971932</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -3706,10 +3694,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C100" t="n">
-        <v>90.8019</v>
+        <v>84.43358251868889</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -3739,10 +3727,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C101" t="n">
-        <v>90.7595</v>
+        <v>86.0636299618935</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -3772,10 +3760,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C102" t="n">
-        <v>89.601</v>
+        <v>90.80194643999999</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -3805,10 +3793,10 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="C103" t="n">
-        <v>91.22110000000001</v>
+        <v>90.75951564</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -3834,14 +3822,14 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>DEU</t>
+          <t>CYP</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="C104" t="n">
-        <v>82</v>
+        <v>89.60099194</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -3867,14 +3855,14 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>DEU</t>
+          <t>CYP</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>2011</v>
+        <v>2023</v>
       </c>
       <c r="C105" t="n">
-        <v>81.27</v>
+        <v>91.22110357</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -3900,14 +3888,14 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>DEU</t>
+          <t>CYP</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>2012</v>
+        <v>2024</v>
       </c>
       <c r="C106" t="n">
-        <v>82.34999999999999</v>
+        <v>89.60099246</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -3937,10 +3925,10 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="C107" t="n">
-        <v>84.17</v>
+        <v>82</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -3970,10 +3958,10 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="C108" t="n">
-        <v>86.19370000000001</v>
+        <v>81.26999953601999</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -4003,10 +3991,10 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="C109" t="n">
-        <v>87.5898</v>
+        <v>82.34999847383919</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -4036,10 +4024,10 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="C110" t="n">
-        <v>84.1652</v>
+        <v>84.17</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -4069,10 +4057,10 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="C111" t="n">
-        <v>84.3942</v>
+        <v>86.1937006578756</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -4102,10 +4090,10 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="C112" t="n">
-        <v>87.0371</v>
+        <v>87.5897993525767</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -4135,10 +4123,10 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="C113" t="n">
-        <v>88.1345</v>
+        <v>84.1652066441212</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -4168,10 +4156,10 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="C114" t="n">
-        <v>89.8129</v>
+        <v>84.39415370108441</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -4201,10 +4189,10 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="C115" t="n">
-        <v>91.4306</v>
+        <v>87.037112092841</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -4234,10 +4222,10 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C116" t="n">
-        <v>91.6298</v>
+        <v>88.1345169091916</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -4267,10 +4255,10 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="C117" t="n">
-        <v>92.4764</v>
+        <v>89.81294133</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -4300,10 +4288,10 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="C118" t="n">
-        <v>93.5</v>
+        <v>91.43060973</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -4329,14 +4317,14 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>DNK</t>
+          <t>DEU</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="C119" t="n">
-        <v>88.72</v>
+        <v>91.62984383</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -4362,14 +4350,14 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>DNK</t>
+          <t>DEU</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>2011</v>
+        <v>2023</v>
       </c>
       <c r="C120" t="n">
-        <v>89.81</v>
+        <v>92.4763763</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -4395,14 +4383,14 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>DNK</t>
+          <t>DEU</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>2012</v>
+        <v>2024</v>
       </c>
       <c r="C121" t="n">
-        <v>92.26000000000001</v>
+        <v>93.49999579</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -4432,10 +4420,10 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="C122" t="n">
-        <v>94.6297</v>
+        <v>88.72</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -4465,10 +4453,10 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="C123" t="n">
-        <v>95.9935</v>
+        <v>89.81001338952321</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -4498,10 +4486,10 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="C124" t="n">
-        <v>96.3305</v>
+        <v>92.2600117153012</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -4531,10 +4519,10 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="C125" t="n">
-        <v>96.9678</v>
+        <v>94.6297</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -4564,10 +4552,10 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="C126" t="n">
-        <v>97.0994</v>
+        <v>95.9935053764454</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -4597,10 +4585,10 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="C127" t="n">
-        <v>97.3192</v>
+        <v>96.3305016195436</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -4630,10 +4618,10 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="C128" t="n">
-        <v>98.04640000000001</v>
+        <v>96.96778525166449</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -4663,10 +4651,10 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="C129" t="n">
-        <v>96.5491</v>
+        <v>97.0993621555621</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -4696,10 +4684,10 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="C130" t="n">
-        <v>98.8659</v>
+        <v>97.31920436510021</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -4729,10 +4717,10 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C131" t="n">
-        <v>97.8601</v>
+        <v>98.04643475215489</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -4762,10 +4750,10 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="C132" t="n">
-        <v>98.7756</v>
+        <v>96.54914573000001</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -4795,10 +4783,10 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="C133" t="n">
-        <v>99.7692</v>
+        <v>98.8658506</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -4824,14 +4812,14 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>DNK</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="C134" t="n">
-        <v>65.8</v>
+        <v>97.86011812</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -4857,14 +4845,14 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>DNK</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>2011</v>
+        <v>2023</v>
       </c>
       <c r="C135" t="n">
-        <v>67.09</v>
+        <v>98.77559196999999</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -4890,14 +4878,14 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>DNK</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>2012</v>
+        <v>2024</v>
       </c>
       <c r="C136" t="n">
-        <v>69.81</v>
+        <v>99.76915157000001</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -4927,10 +4915,10 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="C137" t="n">
-        <v>71.63500000000001</v>
+        <v>65.8</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -4960,10 +4948,10 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="C138" t="n">
-        <v>76.1867</v>
+        <v>67.0899993926581</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -4993,10 +4981,10 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="C139" t="n">
-        <v>78.6896</v>
+        <v>69.80999994200241</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -5026,10 +5014,10 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="C140" t="n">
-        <v>80.5613</v>
+        <v>71.63500000000001</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -5059,10 +5047,10 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="C141" t="n">
-        <v>84.6022</v>
+        <v>76.18670897787121</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -5092,10 +5080,10 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="C142" t="n">
-        <v>86.10720000000001</v>
+        <v>78.6896318703515</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -5125,10 +5113,10 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="C143" t="n">
-        <v>90.7187</v>
+        <v>80.56133294321791</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -5158,10 +5146,10 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="C144" t="n">
-        <v>93.2056</v>
+        <v>84.60224570165239</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -5191,10 +5179,10 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="C145" t="n">
-        <v>93.89749999999999</v>
+        <v>86.10723552565899</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -5224,10 +5212,10 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C146" t="n">
-        <v>94.4855</v>
+        <v>90.718665325267</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -5257,10 +5245,10 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="C147" t="n">
-        <v>95.4456</v>
+        <v>93.20564892</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -5290,10 +5278,10 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="C148" t="n">
-        <v>95.75749999999999</v>
+        <v>93.89752156999999</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -5319,14 +5307,14 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>EST</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="C149" t="n">
-        <v>74.09999999999999</v>
+        <v>94.4855432</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -5352,14 +5340,14 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>EST</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>2011</v>
+        <v>2023</v>
       </c>
       <c r="C150" t="n">
-        <v>76.5</v>
+        <v>95.44564516</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -5385,14 +5373,14 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>EST</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>2012</v>
+        <v>2024</v>
       </c>
       <c r="C151" t="n">
-        <v>78.3899</v>
+        <v>95.7574516</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -5422,10 +5410,10 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="C152" t="n">
-        <v>80.0043</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -5455,10 +5443,10 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="C153" t="n">
-        <v>84.2415</v>
+        <v>76.5</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -5488,10 +5476,10 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="C154" t="n">
-        <v>88.4097</v>
+        <v>78.38992592592589</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -5521,10 +5509,10 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="C155" t="n">
-        <v>87.2402</v>
+        <v>80.0043</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -5554,10 +5542,10 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="C156" t="n">
-        <v>88.10250000000001</v>
+        <v>84.2415280294352</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -5587,10 +5575,10 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="C157" t="n">
-        <v>89.357</v>
+        <v>88.40970350404309</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -5620,10 +5608,10 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="C158" t="n">
-        <v>90.2289</v>
+        <v>87.2402327514547</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -5653,10 +5641,10 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="C159" t="n">
-        <v>89.0583</v>
+        <v>88.10245687401989</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -5686,10 +5674,10 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="C160" t="n">
-        <v>90.97969999999999</v>
+        <v>89.3570077747426</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -5719,10 +5707,10 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C161" t="n">
-        <v>91.5202</v>
+        <v>90.22892819979189</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -5752,10 +5740,10 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="C162" t="n">
-        <v>93.18340000000001</v>
+        <v>89.05828665999999</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -5785,10 +5773,10 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="C163" t="n">
-        <v>92.238</v>
+        <v>90.97970174</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -5814,14 +5802,14 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>EST</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="C164" t="n">
-        <v>77.28</v>
+        <v>91.52016546</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -5847,14 +5835,14 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>EST</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>2011</v>
+        <v>2023</v>
       </c>
       <c r="C165" t="n">
-        <v>77.81999999999999</v>
+        <v>93.18342241000001</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -5880,14 +5868,14 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>EST</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>2012</v>
+        <v>2024</v>
       </c>
       <c r="C166" t="n">
-        <v>81.44</v>
+        <v>92.23796204</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -5917,10 +5905,10 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="C167" t="n">
-        <v>81.9198</v>
+        <v>77.28</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -5950,10 +5938,10 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="C168" t="n">
-        <v>83.75109999999999</v>
+        <v>77.81999899267061</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -5983,10 +5971,10 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="C169" t="n">
-        <v>78.006</v>
+        <v>81.44</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -6016,10 +6004,10 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="C170" t="n">
-        <v>79.2698</v>
+        <v>81.9198</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -6049,10 +6037,10 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="C171" t="n">
-        <v>80.5025</v>
+        <v>83.75109966818211</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -6082,10 +6070,10 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="C172" t="n">
-        <v>82.0432</v>
+        <v>78.0060377071902</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -6115,10 +6103,10 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="C173" t="n">
-        <v>83.33969999999999</v>
+        <v>79.2698113207547</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -6148,10 +6136,10 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="C174" t="n">
-        <v>84.7064</v>
+        <v>80.5024597243607</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -6181,10 +6169,10 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="C175" t="n">
-        <v>86.0955</v>
+        <v>82.04318677884839</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -6214,10 +6202,10 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C176" t="n">
-        <v>85.33329999999999</v>
+        <v>83.3397440866883</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -6247,10 +6235,10 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="C177" t="n">
-        <v>86.8364</v>
+        <v>84.70639801</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -6280,10 +6268,10 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="C178" t="n">
-        <v>88.6538</v>
+        <v>86.09548574999999</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -6309,14 +6297,14 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>FIN</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="C179" t="n">
-        <v>86.89</v>
+        <v>85.33331733999999</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -6342,14 +6330,14 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>FIN</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>2011</v>
+        <v>2023</v>
       </c>
       <c r="C180" t="n">
-        <v>88.70999999999999</v>
+        <v>86.83635789</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -6375,14 +6363,14 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>FIN</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>2012</v>
+        <v>2024</v>
       </c>
       <c r="C181" t="n">
-        <v>89.88</v>
+        <v>88.65381637999999</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -6412,10 +6400,10 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="C182" t="n">
-        <v>91.51439999999999</v>
+        <v>86.89</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -6445,10 +6433,10 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="C183" t="n">
-        <v>86.5304</v>
+        <v>88.70999491353</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -6478,10 +6466,10 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="C184" t="n">
-        <v>86.4221</v>
+        <v>89.87999797422199</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -6511,10 +6499,10 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="C185" t="n">
-        <v>87.70359999999999</v>
+        <v>91.51439999999999</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -6544,10 +6532,10 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="C186" t="n">
-        <v>87.4689</v>
+        <v>86.5303927529377</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -6577,10 +6565,10 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="C187" t="n">
-        <v>88.89</v>
+        <v>86.4221333325445</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -6610,10 +6598,10 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="C188" t="n">
-        <v>89.6074</v>
+        <v>87.70364995994549</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -6643,10 +6631,10 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="C189" t="n">
-        <v>92.1703</v>
+        <v>87.4689290730615</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -6676,10 +6664,10 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="C190" t="n">
-        <v>92.8081</v>
+        <v>88.8899599985585</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -6709,10 +6697,10 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C191" t="n">
-        <v>92.9888</v>
+        <v>89.60738511297789</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -6742,10 +6730,10 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="C192" t="n">
-        <v>93.51390000000001</v>
+        <v>92.17027106</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -6771,14 +6759,14 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>GRC</t>
+          <t>FIN</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>2010</v>
+        <v>2021</v>
       </c>
       <c r="C193" t="n">
-        <v>44.4</v>
+        <v>92.80806081999999</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -6804,14 +6792,14 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>GRC</t>
+          <t>FIN</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>2011</v>
+        <v>2022</v>
       </c>
       <c r="C194" t="n">
-        <v>51.65</v>
+        <v>92.98879470999999</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -6837,14 +6825,14 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>GRC</t>
+          <t>FIN</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>2012</v>
+        <v>2023</v>
       </c>
       <c r="C195" t="n">
-        <v>55.07</v>
+        <v>93.51385075</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -6870,14 +6858,14 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>GRC</t>
+          <t>FIN</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>2013</v>
+        <v>2024</v>
       </c>
       <c r="C196" t="n">
-        <v>59.8663</v>
+        <v>93.72405196</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -6907,10 +6895,10 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C197" t="n">
-        <v>63.2073</v>
+        <v>44.4</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -6940,10 +6928,10 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>2015</v>
+        <v>2011</v>
       </c>
       <c r="C198" t="n">
-        <v>66.83499999999999</v>
+        <v>51.6499951676815</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -6973,10 +6961,10 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C199" t="n">
-        <v>69.0879</v>
+        <v>55.0699934418411</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -7006,10 +6994,10 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>2017</v>
+        <v>2013</v>
       </c>
       <c r="C200" t="n">
-        <v>69.893</v>
+        <v>59.8663</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -7039,10 +7027,10 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="C201" t="n">
-        <v>72.2384</v>
+        <v>63.2073404784561</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -7072,10 +7060,10 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="C202" t="n">
-        <v>75.6712</v>
+        <v>66.8349594911035</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -7105,10 +7093,10 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="C203" t="n">
-        <v>78.11579999999999</v>
+        <v>69.0879154723892</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -7138,10 +7126,10 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="C204" t="n">
-        <v>78.4943</v>
+        <v>69.89297065431541</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -7171,10 +7159,10 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C205" t="n">
-        <v>83.1707</v>
+        <v>72.2383733920483</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -7204,10 +7192,10 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="C206" t="n">
-        <v>85.0102</v>
+        <v>75.67120669317571</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -7237,10 +7225,10 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="C207" t="n">
-        <v>86.2697</v>
+        <v>78.11584474</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -7266,14 +7254,14 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>HUN</t>
+          <t>GRC</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>2010</v>
+        <v>2021</v>
       </c>
       <c r="C208" t="n">
-        <v>65</v>
+        <v>78.49426371</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -7299,14 +7287,14 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>HUN</t>
+          <t>GRC</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>2011</v>
+        <v>2022</v>
       </c>
       <c r="C209" t="n">
-        <v>68.02</v>
+        <v>83.17066333</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -7332,14 +7320,14 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>HUN</t>
+          <t>GRC</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>2012</v>
+        <v>2023</v>
       </c>
       <c r="C210" t="n">
-        <v>70.58</v>
+        <v>85.0102229</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -7365,14 +7353,14 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>HUN</t>
+          <t>GRC</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>2013</v>
+        <v>2024</v>
       </c>
       <c r="C211" t="n">
-        <v>72.6439</v>
+        <v>86.26968886</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -7402,10 +7390,10 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C212" t="n">
-        <v>75.6532</v>
+        <v>65</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -7435,10 +7423,10 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>2015</v>
+        <v>2011</v>
       </c>
       <c r="C213" t="n">
-        <v>72.8347</v>
+        <v>68.0199878861296</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -7468,10 +7456,10 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C214" t="n">
-        <v>79.2594</v>
+        <v>70.57999815383801</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -7501,10 +7489,10 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>2017</v>
+        <v>2013</v>
       </c>
       <c r="C215" t="n">
-        <v>76.7505</v>
+        <v>72.6439</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -7534,10 +7522,10 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="C216" t="n">
-        <v>76.0744</v>
+        <v>75.6531974544103</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -7567,10 +7555,10 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="C217" t="n">
-        <v>80.3717</v>
+        <v>72.8347370323805</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -7600,10 +7588,10 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="C218" t="n">
-        <v>84.77119999999999</v>
+        <v>79.25941212730569</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -7633,10 +7621,10 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="C219" t="n">
-        <v>88.6408</v>
+        <v>76.75054712019219</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -7666,10 +7654,10 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C220" t="n">
-        <v>89.14279999999999</v>
+        <v>76.0743606365063</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -7699,10 +7687,10 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="C221" t="n">
-        <v>91.45010000000001</v>
+        <v>80.37169360504819</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -7732,10 +7720,10 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="C222" t="n">
-        <v>93.779</v>
+        <v>84.77115202</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -7761,14 +7749,14 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>NLD</t>
+          <t>HUN</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>2010</v>
+        <v>2021</v>
       </c>
       <c r="C223" t="n">
-        <v>90.72</v>
+        <v>88.64083466</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -7794,14 +7782,14 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>NLD</t>
+          <t>HUN</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>2011</v>
+        <v>2022</v>
       </c>
       <c r="C224" t="n">
-        <v>91.42</v>
+        <v>89.14282688</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -7827,14 +7815,14 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>NLD</t>
+          <t>HUN</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>2012</v>
+        <v>2023</v>
       </c>
       <c r="C225" t="n">
-        <v>92.86</v>
+        <v>91.4500713</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -7860,14 +7848,14 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>NLD</t>
+          <t>HUN</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>2013</v>
+        <v>2024</v>
       </c>
       <c r="C226" t="n">
-        <v>93.9564</v>
+        <v>93.77898628</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -7897,10 +7885,10 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C227" t="n">
-        <v>91.66670000000001</v>
+        <v>90.72</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -7930,10 +7918,10 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>2015</v>
+        <v>2011</v>
       </c>
       <c r="C228" t="n">
-        <v>91.72410000000001</v>
+        <v>91.4199957622284</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -7963,10 +7951,10 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C229" t="n">
-        <v>90.411</v>
+        <v>92.85999235952499</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -7996,10 +7984,10 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>2017</v>
+        <v>2013</v>
       </c>
       <c r="C230" t="n">
-        <v>93.1973</v>
+        <v>93.9564</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -8029,10 +8017,10 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="C231" t="n">
-        <v>91.89190000000001</v>
+        <v>91.6666666666667</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -8062,10 +8050,10 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="C232" t="n">
-        <v>93.2886</v>
+        <v>91.72413793103451</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -8095,10 +8083,10 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="C233" t="n">
-        <v>91.33329999999999</v>
+        <v>90.41095890410961</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -8128,10 +8116,10 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="C234" t="n">
-        <v>92.053</v>
+        <v>93.1972789115646</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -8161,10 +8149,10 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C235" t="n">
-        <v>92.5197</v>
+        <v>91.8918918918919</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -8194,10 +8182,10 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="C236" t="n">
-        <v>97.0068</v>
+        <v>93.28859060402689</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -8223,14 +8211,14 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>HRV</t>
+          <t>NLD</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>2010</v>
+        <v>2020</v>
       </c>
       <c r="C237" t="n">
-        <v>56.55</v>
+        <v>91.33333333</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -8256,14 +8244,14 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>HRV</t>
+          <t>NLD</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>2011</v>
+        <v>2021</v>
       </c>
       <c r="C238" t="n">
-        <v>57.79</v>
+        <v>92.05298012999999</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -8289,14 +8277,14 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>HRV</t>
+          <t>NLD</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="C239" t="n">
-        <v>61.94</v>
+        <v>92.51968504</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -8322,14 +8310,14 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>HRV</t>
+          <t>NLD</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>2013</v>
+        <v>2023</v>
       </c>
       <c r="C240" t="n">
-        <v>66.74760000000001</v>
+        <v>97.00680272</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -8355,14 +8343,14 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>HRV</t>
+          <t>NLD</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>2014</v>
+        <v>2024</v>
       </c>
       <c r="C241" t="n">
-        <v>68.56789999999999</v>
+        <v>97.00679778999999</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -8392,10 +8380,10 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>2015</v>
+        <v>2010</v>
       </c>
       <c r="C242" t="n">
-        <v>69.845</v>
+        <v>56.55</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -8425,10 +8413,10 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>2016</v>
+        <v>2011</v>
       </c>
       <c r="C243" t="n">
-        <v>72.6973</v>
+        <v>57.7899789891444</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -8458,10 +8446,10 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="C244" t="n">
-        <v>67.0962</v>
+        <v>61.9399731527956</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -8491,10 +8479,10 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>2018</v>
+        <v>2013</v>
       </c>
       <c r="C245" t="n">
-        <v>75.2946</v>
+        <v>66.74760000000001</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -8524,10 +8512,10 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="C246" t="n">
-        <v>79.07980000000001</v>
+        <v>68.5678992528467</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -8557,10 +8545,10 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="C247" t="n">
-        <v>78.32089999999999</v>
+        <v>69.84503592382811</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -8590,10 +8578,10 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="C248" t="n">
-        <v>81.254</v>
+        <v>72.6972696701463</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -8623,10 +8611,10 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="C249" t="n">
-        <v>82.0716</v>
+        <v>67.0961920368478</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -8656,10 +8644,10 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="C250" t="n">
-        <v>83.24120000000001</v>
+        <v>75.2946259897258</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -8689,10 +8677,10 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="C251" t="n">
-        <v>83.6324</v>
+        <v>79.07978367575539</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -8718,14 +8706,14 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>HRV</t>
         </is>
       </c>
       <c r="B252" t="n">
-        <v>2010</v>
+        <v>2020</v>
       </c>
       <c r="C252" t="n">
-        <v>53.68</v>
+        <v>78.32090004</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -8751,14 +8739,14 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>HRV</t>
         </is>
       </c>
       <c r="B253" t="n">
-        <v>2011</v>
+        <v>2021</v>
       </c>
       <c r="C253" t="n">
-        <v>54.39</v>
+        <v>81.25396608</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -8784,14 +8772,14 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>HRV</t>
         </is>
       </c>
       <c r="B254" t="n">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="C254" t="n">
-        <v>55.83</v>
+        <v>82.07155532</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -8817,14 +8805,14 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>HRV</t>
         </is>
       </c>
       <c r="B255" t="n">
-        <v>2013</v>
+        <v>2023</v>
       </c>
       <c r="C255" t="n">
-        <v>58.4593</v>
+        <v>83.24117599</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -8850,14 +8838,14 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>HRV</t>
         </is>
       </c>
       <c r="B256" t="n">
-        <v>2014</v>
+        <v>2024</v>
       </c>
       <c r="C256" t="n">
-        <v>55.6385</v>
+        <v>83.63240029000001</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -8887,10 +8875,10 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>2015</v>
+        <v>2010</v>
       </c>
       <c r="C257" t="n">
-        <v>58.1417</v>
+        <v>53.68</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -8920,10 +8908,10 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>2016</v>
+        <v>2011</v>
       </c>
       <c r="C258" t="n">
-        <v>61.3243</v>
+        <v>54.3899983018814</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -8953,10 +8941,10 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="C259" t="n">
-        <v>63.0773</v>
+        <v>55.829997993283</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -8986,10 +8974,10 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>2018</v>
+        <v>2013</v>
       </c>
       <c r="C260" t="n">
-        <v>74.38720000000001</v>
+        <v>58.4593</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -9019,10 +9007,10 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="C261" t="n">
-        <v>67.8507</v>
+        <v>55.6384602242293</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -9052,10 +9040,10 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="C262" t="n">
-        <v>70.4834</v>
+        <v>58.1417349568747</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -9085,10 +9073,10 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="C263" t="n">
-        <v>74.8623</v>
+        <v>61.3242527666303</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -9118,10 +9106,10 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="C264" t="n">
-        <v>85.0607</v>
+        <v>63.0773469984291</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -9151,10 +9139,10 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="C265" t="n">
-        <v>87.0278</v>
+        <v>74.3871829234822</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -9184,10 +9172,10 @@
         </is>
       </c>
       <c r="B266" t="n">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="C266" t="n">
-        <v>89.22069999999999</v>
+        <v>67.85071028748359</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -9213,14 +9201,14 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>IRL</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="B267" t="n">
-        <v>2010</v>
+        <v>2020</v>
       </c>
       <c r="C267" t="n">
-        <v>69.84999999999999</v>
+        <v>70.48342785</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -9246,14 +9234,14 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>IRL</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="B268" t="n">
-        <v>2011</v>
+        <v>2021</v>
       </c>
       <c r="C268" t="n">
-        <v>74.89</v>
+        <v>74.8623274</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -9279,14 +9267,14 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>IRL</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="B269" t="n">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="C269" t="n">
-        <v>76.92</v>
+        <v>85.06074504</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -9312,14 +9300,14 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>IRL</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="B270" t="n">
-        <v>2013</v>
+        <v>2023</v>
       </c>
       <c r="C270" t="n">
-        <v>78.24769999999999</v>
+        <v>87.0278292</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -9345,14 +9333,14 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>IRL</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="B271" t="n">
-        <v>2014</v>
+        <v>2024</v>
       </c>
       <c r="C271" t="n">
-        <v>83.49169999999999</v>
+        <v>89.2207202</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -9382,10 +9370,10 @@
         </is>
       </c>
       <c r="B272" t="n">
-        <v>2015</v>
+        <v>2010</v>
       </c>
       <c r="C272" t="n">
-        <v>83.4948</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -9415,10 +9403,10 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>2016</v>
+        <v>2011</v>
       </c>
       <c r="C273" t="n">
-        <v>83.5</v>
+        <v>74.88997296709439</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -9448,10 +9436,10 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="C274" t="n">
-        <v>84.114</v>
+        <v>76.919992540097</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -9481,10 +9469,10 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>2018</v>
+        <v>2013</v>
       </c>
       <c r="C275" t="n">
-        <v>87.0001</v>
+        <v>78.24769999999999</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -9514,10 +9502,10 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="C276" t="n">
-        <v>87.0001</v>
+        <v>83.4917223351728</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -9547,10 +9535,10 @@
         </is>
       </c>
       <c r="B277" t="n">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="C277" t="n">
-        <v>91.9999</v>
+        <v>83.4947916666667</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -9580,10 +9568,10 @@
         </is>
       </c>
       <c r="B278" t="n">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="C278" t="n">
-        <v>96.4235</v>
+        <v>83.5</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -9613,10 +9601,10 @@
         </is>
       </c>
       <c r="B279" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="C279" t="n">
-        <v>96.6206</v>
+        <v>84.1140070623844</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -9646,10 +9634,10 @@
         </is>
       </c>
       <c r="B280" t="n">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="C280" t="n">
-        <v>96.4974</v>
+        <v>87.00014011489419</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -9675,14 +9663,14 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>LTU</t>
+          <t>IRL</t>
         </is>
       </c>
       <c r="B281" t="n">
-        <v>2010</v>
+        <v>2019</v>
       </c>
       <c r="C281" t="n">
-        <v>62.12</v>
+        <v>87.00005524251461</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -9708,14 +9696,14 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>LTU</t>
+          <t>IRL</t>
         </is>
       </c>
       <c r="B282" t="n">
-        <v>2011</v>
+        <v>2020</v>
       </c>
       <c r="C282" t="n">
-        <v>63.64</v>
+        <v>91.99989097</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -9741,14 +9729,14 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>LTU</t>
+          <t>IRL</t>
         </is>
       </c>
       <c r="B283" t="n">
-        <v>2012</v>
+        <v>2021</v>
       </c>
       <c r="C283" t="n">
-        <v>67.23</v>
+        <v>93.50610352</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -9774,14 +9762,14 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>LTU</t>
+          <t>IRL</t>
         </is>
       </c>
       <c r="B284" t="n">
-        <v>2013</v>
+        <v>2022</v>
       </c>
       <c r="C284" t="n">
-        <v>68.4529</v>
+        <v>95.03690338</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -9807,14 +9795,14 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>LTU</t>
+          <t>IRL</t>
         </is>
       </c>
       <c r="B285" t="n">
-        <v>2014</v>
+        <v>2023</v>
       </c>
       <c r="C285" t="n">
-        <v>72.1335</v>
+        <v>96.8660965</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -9840,14 +9828,14 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>LTU</t>
+          <t>IRL</t>
         </is>
       </c>
       <c r="B286" t="n">
-        <v>2015</v>
+        <v>2024</v>
       </c>
       <c r="C286" t="n">
-        <v>71.3781</v>
+        <v>97.18769836</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -9877,10 +9865,10 @@
         </is>
       </c>
       <c r="B287" t="n">
-        <v>2016</v>
+        <v>2010</v>
       </c>
       <c r="C287" t="n">
-        <v>74.3766</v>
+        <v>62.12</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -9910,10 +9898,10 @@
         </is>
       </c>
       <c r="B288" t="n">
-        <v>2017</v>
+        <v>2011</v>
       </c>
       <c r="C288" t="n">
-        <v>77.6153</v>
+        <v>63.6399774002179</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -9943,10 +9931,10 @@
         </is>
       </c>
       <c r="B289" t="n">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="C289" t="n">
-        <v>79.7226</v>
+        <v>67.22998932764141</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -9976,10 +9964,10 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>2019</v>
+        <v>2013</v>
       </c>
       <c r="C290" t="n">
-        <v>81.5819</v>
+        <v>68.4529</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -10009,10 +9997,10 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>2020</v>
+        <v>2014</v>
       </c>
       <c r="C291" t="n">
-        <v>83.05549999999999</v>
+        <v>72.1335378644566</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -10042,10 +10030,10 @@
         </is>
       </c>
       <c r="B292" t="n">
-        <v>2021</v>
+        <v>2015</v>
       </c>
       <c r="C292" t="n">
-        <v>86.93049999999999</v>
+        <v>71.37805901017541</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -10075,10 +10063,10 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="C293" t="n">
-        <v>87.7242</v>
+        <v>74.3766455618662</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -10108,10 +10096,10 @@
         </is>
       </c>
       <c r="B294" t="n">
-        <v>2023</v>
+        <v>2017</v>
       </c>
       <c r="C294" t="n">
-        <v>88.5029</v>
+        <v>77.6152565124514</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -10137,14 +10125,14 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>LUX</t>
+          <t>LTU</t>
         </is>
       </c>
       <c r="B295" t="n">
-        <v>2010</v>
+        <v>2018</v>
       </c>
       <c r="C295" t="n">
-        <v>90.62</v>
+        <v>79.72258276805179</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -10170,14 +10158,14 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>LUX</t>
+          <t>LTU</t>
         </is>
       </c>
       <c r="B296" t="n">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="C296" t="n">
-        <v>90.0299</v>
+        <v>81.5818683764046</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -10203,14 +10191,14 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>LUX</t>
+          <t>LTU</t>
         </is>
       </c>
       <c r="B297" t="n">
-        <v>2012</v>
+        <v>2020</v>
       </c>
       <c r="C297" t="n">
-        <v>91.9499</v>
+        <v>83.05554724</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -10236,14 +10224,14 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>LUX</t>
+          <t>LTU</t>
         </is>
       </c>
       <c r="B298" t="n">
-        <v>2013</v>
+        <v>2021</v>
       </c>
       <c r="C298" t="n">
-        <v>93.7765</v>
+        <v>86.93054425</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -10269,14 +10257,14 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>LUX</t>
+          <t>LTU</t>
         </is>
       </c>
       <c r="B299" t="n">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="C299" t="n">
-        <v>94.67019999999999</v>
+        <v>87.72420219</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -10302,14 +10290,14 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>LUX</t>
+          <t>LTU</t>
         </is>
       </c>
       <c r="B300" t="n">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="C300" t="n">
-        <v>96.3767</v>
+        <v>88.50287484</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -10335,14 +10323,14 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>LUX</t>
+          <t>LTU</t>
         </is>
       </c>
       <c r="B301" t="n">
-        <v>2016</v>
+        <v>2024</v>
       </c>
       <c r="C301" t="n">
-        <v>98.1367</v>
+        <v>89.16116293</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -10372,10 +10360,10 @@
         </is>
       </c>
       <c r="B302" t="n">
-        <v>2017</v>
+        <v>2010</v>
       </c>
       <c r="C302" t="n">
-        <v>97.363</v>
+        <v>90.62</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -10405,10 +10393,10 @@
         </is>
       </c>
       <c r="B303" t="n">
-        <v>2018</v>
+        <v>2011</v>
       </c>
       <c r="C303" t="n">
-        <v>97.0613</v>
+        <v>90.0298585646936</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -10438,10 +10426,10 @@
         </is>
       </c>
       <c r="B304" t="n">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="C304" t="n">
-        <v>97.1206</v>
+        <v>91.9499237417387</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -10471,10 +10459,10 @@
         </is>
       </c>
       <c r="B305" t="n">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="C305" t="n">
-        <v>98.45959999999999</v>
+        <v>93.7765</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -10504,10 +10492,10 @@
         </is>
       </c>
       <c r="B306" t="n">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="C306" t="n">
-        <v>98.6609</v>
+        <v>94.6702052774766</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -10537,10 +10525,10 @@
         </is>
       </c>
       <c r="B307" t="n">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="C307" t="n">
-        <v>98.242</v>
+        <v>96.37671417047591</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -10570,10 +10558,10 @@
         </is>
       </c>
       <c r="B308" t="n">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="C308" t="n">
-        <v>99.3479</v>
+        <v>98.1366986657616</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -10603,10 +10591,10 @@
         </is>
       </c>
       <c r="B309" t="n">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="C309" t="n">
-        <v>98.7606</v>
+        <v>97.36296032417511</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -10632,14 +10620,14 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>LVA</t>
+          <t>LUX</t>
         </is>
       </c>
       <c r="B310" t="n">
-        <v>2010</v>
+        <v>2018</v>
       </c>
       <c r="C310" t="n">
-        <v>68.42</v>
+        <v>97.061298705829</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -10665,14 +10653,14 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>LVA</t>
+          <t>LUX</t>
         </is>
       </c>
       <c r="B311" t="n">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="C311" t="n">
-        <v>69.75</v>
+        <v>97.12063569327201</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -10698,14 +10686,14 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>LVA</t>
+          <t>LUX</t>
         </is>
       </c>
       <c r="B312" t="n">
-        <v>2012</v>
+        <v>2020</v>
       </c>
       <c r="C312" t="n">
-        <v>73.1199</v>
+        <v>98.45962892999999</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -10731,14 +10719,14 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>LVA</t>
+          <t>LUX</t>
         </is>
       </c>
       <c r="B313" t="n">
-        <v>2013</v>
+        <v>2021</v>
       </c>
       <c r="C313" t="n">
-        <v>75.23439999999999</v>
+        <v>98.66086333</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -10764,14 +10752,14 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>LVA</t>
+          <t>LUX</t>
         </is>
       </c>
       <c r="B314" t="n">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="C314" t="n">
-        <v>75.8261</v>
+        <v>98.24203749</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -10797,14 +10785,14 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>LVA</t>
+          <t>LUX</t>
         </is>
       </c>
       <c r="B315" t="n">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="C315" t="n">
-        <v>79.20059999999999</v>
+        <v>99.34785707</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -10830,14 +10818,14 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>LVA</t>
+          <t>LUX</t>
         </is>
       </c>
       <c r="B316" t="n">
-        <v>2016</v>
+        <v>2024</v>
       </c>
       <c r="C316" t="n">
-        <v>79.8421</v>
+        <v>98.7606147</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -10867,10 +10855,10 @@
         </is>
       </c>
       <c r="B317" t="n">
-        <v>2017</v>
+        <v>2010</v>
       </c>
       <c r="C317" t="n">
-        <v>80.11409999999999</v>
+        <v>68.42</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -10900,10 +10888,10 @@
         </is>
       </c>
       <c r="B318" t="n">
-        <v>2018</v>
+        <v>2011</v>
       </c>
       <c r="C318" t="n">
-        <v>83.5772</v>
+        <v>69.74995455922451</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -10933,10 +10921,10 @@
         </is>
       </c>
       <c r="B319" t="n">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="C319" t="n">
-        <v>86.13549999999999</v>
+        <v>73.1199437663748</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -10966,10 +10954,10 @@
         </is>
       </c>
       <c r="B320" t="n">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="C320" t="n">
-        <v>88.898</v>
+        <v>75.23439999999999</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -10999,10 +10987,10 @@
         </is>
       </c>
       <c r="B321" t="n">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="C321" t="n">
-        <v>91.17959999999999</v>
+        <v>75.8261041383556</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -11032,10 +11020,10 @@
         </is>
       </c>
       <c r="B322" t="n">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="C322" t="n">
-        <v>91.0301</v>
+        <v>79.20058292393441</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -11065,10 +11053,10 @@
         </is>
       </c>
       <c r="B323" t="n">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="C323" t="n">
-        <v>92.1879</v>
+        <v>79.8420977843089</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -11098,10 +11086,10 @@
         </is>
       </c>
       <c r="B324" t="n">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="C324" t="n">
-        <v>92.7076</v>
+        <v>80.1140770037369</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -11127,14 +11115,14 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>MLT</t>
+          <t>LVA</t>
         </is>
       </c>
       <c r="B325" t="n">
-        <v>2010</v>
+        <v>2018</v>
       </c>
       <c r="C325" t="n">
-        <v>63</v>
+        <v>83.57717486309561</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -11160,14 +11148,14 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>MLT</t>
+          <t>LVA</t>
         </is>
       </c>
       <c r="B326" t="n">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="C326" t="n">
-        <v>68.0198</v>
+        <v>86.13545644343</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -11193,14 +11181,14 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>MLT</t>
+          <t>LVA</t>
         </is>
       </c>
       <c r="B327" t="n">
-        <v>2012</v>
+        <v>2020</v>
       </c>
       <c r="C327" t="n">
-        <v>68.1999</v>
+        <v>88.89796078000001</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -11226,14 +11214,14 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>MLT</t>
+          <t>LVA</t>
         </is>
       </c>
       <c r="B328" t="n">
-        <v>2013</v>
+        <v>2021</v>
       </c>
       <c r="C328" t="n">
-        <v>68.91379999999999</v>
+        <v>91.17964988</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -11259,14 +11247,14 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>MLT</t>
+          <t>LVA</t>
         </is>
       </c>
       <c r="B329" t="n">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="C329" t="n">
-        <v>73.11409999999999</v>
+        <v>91.03009059</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -11292,14 +11280,14 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>MLT</t>
+          <t>LVA</t>
         </is>
       </c>
       <c r="B330" t="n">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="C330" t="n">
-        <v>75.95999999999999</v>
+        <v>92.18791290999999</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -11325,14 +11313,14 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>MLT</t>
+          <t>LVA</t>
         </is>
       </c>
       <c r="B331" t="n">
-        <v>2016</v>
+        <v>2024</v>
       </c>
       <c r="C331" t="n">
-        <v>78.07510000000001</v>
+        <v>92.70757011000001</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -11362,10 +11350,10 @@
         </is>
       </c>
       <c r="B332" t="n">
-        <v>2017</v>
+        <v>2010</v>
       </c>
       <c r="C332" t="n">
-        <v>81.0119</v>
+        <v>63</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -11395,10 +11383,10 @@
         </is>
       </c>
       <c r="B333" t="n">
-        <v>2018</v>
+        <v>2011</v>
       </c>
       <c r="C333" t="n">
-        <v>81.658</v>
+        <v>68.0198237885462</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -11428,10 +11416,10 @@
         </is>
       </c>
       <c r="B334" t="n">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="C334" t="n">
-        <v>85.7786</v>
+        <v>68.1998742928975</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -11461,10 +11449,10 @@
         </is>
       </c>
       <c r="B335" t="n">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="C335" t="n">
-        <v>86.8588</v>
+        <v>68.91379999999999</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -11494,10 +11482,10 @@
         </is>
       </c>
       <c r="B336" t="n">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="C336" t="n">
-        <v>87.46980000000001</v>
+        <v>73.1141157845193</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -11527,10 +11515,10 @@
         </is>
       </c>
       <c r="B337" t="n">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="C337" t="n">
-        <v>91.5406</v>
+        <v>75.96001897527471</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -11560,10 +11548,10 @@
         </is>
       </c>
       <c r="B338" t="n">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="C338" t="n">
-        <v>92.0727</v>
+        <v>78.0751488032182</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -11589,14 +11577,14 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>MLT</t>
         </is>
       </c>
       <c r="B339" t="n">
-        <v>2010</v>
+        <v>2017</v>
       </c>
       <c r="C339" t="n">
-        <v>62.32</v>
+        <v>81.0119110762945</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -11622,14 +11610,14 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>MLT</t>
         </is>
       </c>
       <c r="B340" t="n">
-        <v>2011</v>
+        <v>2018</v>
       </c>
       <c r="C340" t="n">
-        <v>61.95</v>
+        <v>81.65804429280141</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -11655,14 +11643,14 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>MLT</t>
         </is>
       </c>
       <c r="B341" t="n">
-        <v>2012</v>
+        <v>2019</v>
       </c>
       <c r="C341" t="n">
-        <v>62.31</v>
+        <v>85.7785963798031</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -11688,14 +11676,14 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>MLT</t>
         </is>
       </c>
       <c r="B342" t="n">
-        <v>2013</v>
+        <v>2020</v>
       </c>
       <c r="C342" t="n">
-        <v>62.8492</v>
+        <v>86.85876183000001</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -11721,14 +11709,14 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>MLT</t>
         </is>
       </c>
       <c r="B343" t="n">
-        <v>2014</v>
+        <v>2021</v>
       </c>
       <c r="C343" t="n">
-        <v>66.59869999999999</v>
+        <v>87.46977742</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -11754,14 +11742,14 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>MLT</t>
         </is>
       </c>
       <c r="B344" t="n">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="C344" t="n">
-        <v>67.997</v>
+        <v>91.54062209</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -11787,14 +11775,14 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>MLT</t>
         </is>
       </c>
       <c r="B345" t="n">
-        <v>2016</v>
+        <v>2023</v>
       </c>
       <c r="C345" t="n">
-        <v>73.30070000000001</v>
+        <v>92.07266941</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -11820,14 +11808,14 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>MLT</t>
         </is>
       </c>
       <c r="B346" t="n">
-        <v>2017</v>
+        <v>2024</v>
       </c>
       <c r="C346" t="n">
-        <v>75.9854</v>
+        <v>93.86029816</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -11857,10 +11845,10 @@
         </is>
       </c>
       <c r="B347" t="n">
-        <v>2018</v>
+        <v>2010</v>
       </c>
       <c r="C347" t="n">
-        <v>77.54170000000001</v>
+        <v>62.32</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -11890,10 +11878,10 @@
         </is>
       </c>
       <c r="B348" t="n">
-        <v>2019</v>
+        <v>2011</v>
       </c>
       <c r="C348" t="n">
-        <v>80.4359</v>
+        <v>61.94999896898</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -11923,10 +11911,10 @@
         </is>
       </c>
       <c r="B349" t="n">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="C349" t="n">
-        <v>83.1849</v>
+        <v>62.3099972714691</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -11956,10 +11944,10 @@
         </is>
       </c>
       <c r="B350" t="n">
-        <v>2021</v>
+        <v>2013</v>
       </c>
       <c r="C350" t="n">
-        <v>85.3749</v>
+        <v>62.8492</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -11989,10 +11977,10 @@
         </is>
       </c>
       <c r="B351" t="n">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="C351" t="n">
-        <v>86.94110000000001</v>
+        <v>66.5987360557248</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -12022,10 +12010,10 @@
         </is>
       </c>
       <c r="B352" t="n">
-        <v>2023</v>
+        <v>2015</v>
       </c>
       <c r="C352" t="n">
-        <v>86.4147</v>
+        <v>67.99698715564151</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -12055,10 +12043,10 @@
         </is>
       </c>
       <c r="B353" t="n">
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="C353" t="n">
-        <v>88.58499999999999</v>
+        <v>73.3007040962669</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -12084,14 +12072,14 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>PRT</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="B354" t="n">
-        <v>2010</v>
+        <v>2017</v>
       </c>
       <c r="C354" t="n">
-        <v>53.3</v>
+        <v>75.98536594938319</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -12117,14 +12105,14 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>PRT</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="B355" t="n">
-        <v>2011</v>
+        <v>2018</v>
       </c>
       <c r="C355" t="n">
-        <v>55.25</v>
+        <v>77.5417345350006</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -12150,14 +12138,14 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>PRT</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="B356" t="n">
-        <v>2012</v>
+        <v>2019</v>
       </c>
       <c r="C356" t="n">
-        <v>60.34</v>
+        <v>80.43590687686731</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -12183,14 +12171,14 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>PRT</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="B357" t="n">
-        <v>2013</v>
+        <v>2020</v>
       </c>
       <c r="C357" t="n">
-        <v>62.0956</v>
+        <v>83.18488714999999</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -12216,14 +12204,14 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>PRT</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="B358" t="n">
-        <v>2014</v>
+        <v>2021</v>
       </c>
       <c r="C358" t="n">
-        <v>64.5924</v>
+        <v>85.37490905999999</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -12249,14 +12237,14 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>PRT</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="B359" t="n">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="C359" t="n">
-        <v>68.63290000000001</v>
+        <v>86.94113479000001</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -12282,14 +12270,14 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>PRT</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="B360" t="n">
-        <v>2016</v>
+        <v>2023</v>
       </c>
       <c r="C360" t="n">
-        <v>70.42359999999999</v>
+        <v>86.414744</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -12315,14 +12303,14 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>PRT</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="B361" t="n">
-        <v>2017</v>
+        <v>2024</v>
       </c>
       <c r="C361" t="n">
-        <v>73.7912</v>
+        <v>88.58496366999999</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -12352,10 +12340,10 @@
         </is>
       </c>
       <c r="B362" t="n">
-        <v>2018</v>
+        <v>2010</v>
       </c>
       <c r="C362" t="n">
-        <v>74.661</v>
+        <v>53.3</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -12385,10 +12373,10 @@
         </is>
       </c>
       <c r="B363" t="n">
-        <v>2019</v>
+        <v>2011</v>
       </c>
       <c r="C363" t="n">
-        <v>75.3464</v>
+        <v>55.2499968797194</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -12418,10 +12406,10 @@
         </is>
       </c>
       <c r="B364" t="n">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="C364" t="n">
-        <v>78.2617</v>
+        <v>60.3399974868057</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -12451,10 +12439,10 @@
         </is>
       </c>
       <c r="B365" t="n">
-        <v>2021</v>
+        <v>2013</v>
       </c>
       <c r="C365" t="n">
-        <v>82.309</v>
+        <v>62.0956</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -12484,10 +12472,10 @@
         </is>
       </c>
       <c r="B366" t="n">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="C366" t="n">
-        <v>84.4969</v>
+        <v>64.5924200648949</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -12517,10 +12505,10 @@
         </is>
       </c>
       <c r="B367" t="n">
-        <v>2023</v>
+        <v>2015</v>
       </c>
       <c r="C367" t="n">
-        <v>85.7901</v>
+        <v>68.6328614804299</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -12550,10 +12538,10 @@
         </is>
       </c>
       <c r="B368" t="n">
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="C368" t="n">
-        <v>88.48699999999999</v>
+        <v>70.423567088723</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -12579,14 +12567,14 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>ROU</t>
+          <t>PRT</t>
         </is>
       </c>
       <c r="B369" t="n">
-        <v>2010</v>
+        <v>2017</v>
       </c>
       <c r="C369" t="n">
-        <v>39.93</v>
+        <v>73.7912139515729</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -12612,14 +12600,14 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>ROU</t>
+          <t>PRT</t>
         </is>
       </c>
       <c r="B370" t="n">
-        <v>2011</v>
+        <v>2018</v>
       </c>
       <c r="C370" t="n">
-        <v>40.01</v>
+        <v>74.6609681487507</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -12645,14 +12633,14 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>ROU</t>
+          <t>PRT</t>
         </is>
       </c>
       <c r="B371" t="n">
-        <v>2012</v>
+        <v>2019</v>
       </c>
       <c r="C371" t="n">
-        <v>45.88</v>
+        <v>75.34637794087121</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -12678,14 +12666,14 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>ROU</t>
+          <t>PRT</t>
         </is>
       </c>
       <c r="B372" t="n">
-        <v>2013</v>
+        <v>2020</v>
       </c>
       <c r="C372" t="n">
-        <v>49.7645</v>
+        <v>78.26166044</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -12711,14 +12699,14 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>ROU</t>
+          <t>PRT</t>
         </is>
       </c>
       <c r="B373" t="n">
-        <v>2014</v>
+        <v>2021</v>
       </c>
       <c r="C373" t="n">
-        <v>54.0783</v>
+        <v>82.30902804</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -12744,14 +12732,14 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>ROU</t>
+          <t>PRT</t>
         </is>
       </c>
       <c r="B374" t="n">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="C374" t="n">
-        <v>55.7632</v>
+        <v>84.49690644</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -12777,14 +12765,14 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>ROU</t>
+          <t>PRT</t>
         </is>
       </c>
       <c r="B375" t="n">
-        <v>2016</v>
+        <v>2023</v>
       </c>
       <c r="C375" t="n">
-        <v>59.504</v>
+        <v>85.79012676000001</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -12810,14 +12798,14 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>ROU</t>
+          <t>PRT</t>
         </is>
       </c>
       <c r="B376" t="n">
-        <v>2017</v>
+        <v>2024</v>
       </c>
       <c r="C376" t="n">
-        <v>63.7473</v>
+        <v>88.48704454</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -12847,10 +12835,10 @@
         </is>
       </c>
       <c r="B377" t="n">
-        <v>2018</v>
+        <v>2010</v>
       </c>
       <c r="C377" t="n">
-        <v>70.68129999999999</v>
+        <v>39.93</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -12880,10 +12868,10 @@
         </is>
       </c>
       <c r="B378" t="n">
-        <v>2019</v>
+        <v>2011</v>
       </c>
       <c r="C378" t="n">
-        <v>73.6575</v>
+        <v>40.0099967810008</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -12913,10 +12901,10 @@
         </is>
       </c>
       <c r="B379" t="n">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="C379" t="n">
-        <v>78.45529999999999</v>
+        <v>45.8799942529424</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -12946,10 +12934,10 @@
         </is>
       </c>
       <c r="B380" t="n">
-        <v>2021</v>
+        <v>2013</v>
       </c>
       <c r="C380" t="n">
-        <v>83.5904</v>
+        <v>49.7645</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -12979,10 +12967,10 @@
         </is>
       </c>
       <c r="B381" t="n">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="C381" t="n">
-        <v>85.5031</v>
+        <v>54.0783206550943</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -13012,10 +13000,10 @@
         </is>
       </c>
       <c r="B382" t="n">
-        <v>2023</v>
+        <v>2015</v>
       </c>
       <c r="C382" t="n">
-        <v>89.2034</v>
+        <v>55.7631556336233</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -13045,10 +13033,10 @@
         </is>
       </c>
       <c r="B383" t="n">
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="C383" t="n">
-        <v>91.29049999999999</v>
+        <v>59.5039512852713</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -13074,14 +13062,14 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>SWE</t>
+          <t>ROU</t>
         </is>
       </c>
       <c r="B384" t="n">
-        <v>2010</v>
+        <v>2017</v>
       </c>
       <c r="C384" t="n">
-        <v>90</v>
+        <v>63.7472821822484</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -13107,14 +13095,14 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>SWE</t>
+          <t>ROU</t>
         </is>
       </c>
       <c r="B385" t="n">
-        <v>2011</v>
+        <v>2018</v>
       </c>
       <c r="C385" t="n">
-        <v>92.77</v>
+        <v>70.6812779273268</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -13140,14 +13128,14 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>SWE</t>
+          <t>ROU</t>
         </is>
       </c>
       <c r="B386" t="n">
-        <v>2012</v>
+        <v>2019</v>
       </c>
       <c r="C386" t="n">
-        <v>93.18000000000001</v>
+        <v>73.6574757545465</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -13173,14 +13161,14 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>SWE</t>
+          <t>ROU</t>
         </is>
       </c>
       <c r="B387" t="n">
-        <v>2013</v>
+        <v>2020</v>
       </c>
       <c r="C387" t="n">
-        <v>94.78360000000001</v>
+        <v>78.45526895</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -13206,14 +13194,14 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>SWE</t>
+          <t>ROU</t>
         </is>
       </c>
       <c r="B388" t="n">
-        <v>2014</v>
+        <v>2021</v>
       </c>
       <c r="C388" t="n">
-        <v>92.5236</v>
+        <v>83.59042650000001</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -13239,14 +13227,14 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>SWE</t>
+          <t>ROU</t>
         </is>
       </c>
       <c r="B389" t="n">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="C389" t="n">
-        <v>90.61020000000001</v>
+        <v>85.50309124</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -13272,14 +13260,14 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>SWE</t>
+          <t>ROU</t>
         </is>
       </c>
       <c r="B390" t="n">
-        <v>2016</v>
+        <v>2023</v>
       </c>
       <c r="C390" t="n">
-        <v>89.65089999999999</v>
+        <v>89.20335498</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -13305,14 +13293,14 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>SWE</t>
+          <t>ROU</t>
         </is>
       </c>
       <c r="B391" t="n">
-        <v>2017</v>
+        <v>2024</v>
       </c>
       <c r="C391" t="n">
-        <v>93.0063</v>
+        <v>91.29048551</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -13342,10 +13330,10 @@
         </is>
       </c>
       <c r="B392" t="n">
-        <v>2018</v>
+        <v>2010</v>
       </c>
       <c r="C392" t="n">
-        <v>89.247</v>
+        <v>90</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -13375,10 +13363,10 @@
         </is>
       </c>
       <c r="B393" t="n">
-        <v>2019</v>
+        <v>2011</v>
       </c>
       <c r="C393" t="n">
-        <v>94.49339999999999</v>
+        <v>92.7699860554046</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -13408,10 +13396,10 @@
         </is>
       </c>
       <c r="B394" t="n">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="C394" t="n">
-        <v>94.5394</v>
+        <v>93.1799880065108</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -13441,10 +13429,10 @@
         </is>
       </c>
       <c r="B395" t="n">
-        <v>2021</v>
+        <v>2013</v>
       </c>
       <c r="C395" t="n">
-        <v>94.6703</v>
+        <v>94.78360000000001</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -13474,10 +13462,10 @@
         </is>
       </c>
       <c r="B396" t="n">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="C396" t="n">
-        <v>95.0097</v>
+        <v>92.5236065037579</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -13507,10 +13495,10 @@
         </is>
       </c>
       <c r="B397" t="n">
-        <v>2023</v>
+        <v>2015</v>
       </c>
       <c r="C397" t="n">
-        <v>95.7033</v>
+        <v>90.6101966398616</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -13540,10 +13528,10 @@
         </is>
       </c>
       <c r="B398" t="n">
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="C398" t="n">
-        <v>95.52930000000001</v>
+        <v>89.65094761023551</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -13569,14 +13557,14 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>SVN</t>
+          <t>SWE</t>
         </is>
       </c>
       <c r="B399" t="n">
-        <v>2010</v>
+        <v>2017</v>
       </c>
       <c r="C399" t="n">
-        <v>70</v>
+        <v>93.0062669652127</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -13602,14 +13590,14 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>SVN</t>
+          <t>SWE</t>
         </is>
       </c>
       <c r="B400" t="n">
-        <v>2011</v>
+        <v>2018</v>
       </c>
       <c r="C400" t="n">
-        <v>67.34</v>
+        <v>89.2469631588137</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -13635,14 +13623,14 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>SVN</t>
+          <t>SWE</t>
         </is>
       </c>
       <c r="B401" t="n">
-        <v>2012</v>
+        <v>2019</v>
       </c>
       <c r="C401" t="n">
-        <v>68.34999999999999</v>
+        <v>94.4934434072202</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -13668,14 +13656,14 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>SVN</t>
+          <t>SWE</t>
         </is>
       </c>
       <c r="B402" t="n">
-        <v>2013</v>
+        <v>2020</v>
       </c>
       <c r="C402" t="n">
-        <v>72.6756</v>
+        <v>94.53943122</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -13701,14 +13689,14 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>SVN</t>
+          <t>SWE</t>
         </is>
       </c>
       <c r="B403" t="n">
-        <v>2014</v>
+        <v>2021</v>
       </c>
       <c r="C403" t="n">
-        <v>71.58629999999999</v>
+        <v>94.6703163</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -13734,14 +13722,14 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>SVN</t>
+          <t>SWE</t>
         </is>
       </c>
       <c r="B404" t="n">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="C404" t="n">
-        <v>73.09869999999999</v>
+        <v>95.00970335</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -13767,14 +13755,14 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>SVN</t>
+          <t>SWE</t>
         </is>
       </c>
       <c r="B405" t="n">
-        <v>2016</v>
+        <v>2023</v>
       </c>
       <c r="C405" t="n">
-        <v>75.49850000000001</v>
+        <v>95.70327460999999</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -13800,14 +13788,14 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>SVN</t>
+          <t>SWE</t>
         </is>
       </c>
       <c r="B406" t="n">
-        <v>2017</v>
+        <v>2024</v>
       </c>
       <c r="C406" t="n">
-        <v>78.8854</v>
+        <v>95.52930428000001</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -13837,10 +13825,10 @@
         </is>
       </c>
       <c r="B407" t="n">
-        <v>2018</v>
+        <v>2010</v>
       </c>
       <c r="C407" t="n">
-        <v>79.75</v>
+        <v>70</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -13870,10 +13858,10 @@
         </is>
       </c>
       <c r="B408" t="n">
-        <v>2019</v>
+        <v>2011</v>
       </c>
       <c r="C408" t="n">
-        <v>83.1084</v>
+        <v>67.3399948092396</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -13903,10 +13891,10 @@
         </is>
       </c>
       <c r="B409" t="n">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="C409" t="n">
-        <v>86.60129999999999</v>
+        <v>68.3499745287825</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -13936,10 +13924,10 @@
         </is>
       </c>
       <c r="B410" t="n">
-        <v>2021</v>
+        <v>2013</v>
       </c>
       <c r="C410" t="n">
-        <v>89.004</v>
+        <v>72.6756</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -13969,10 +13957,10 @@
         </is>
       </c>
       <c r="B411" t="n">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="C411" t="n">
-        <v>88.91249999999999</v>
+        <v>71.58625158556011</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -14002,10 +13990,10 @@
         </is>
       </c>
       <c r="B412" t="n">
-        <v>2023</v>
+        <v>2015</v>
       </c>
       <c r="C412" t="n">
-        <v>90.3779</v>
+        <v>73.0986599745829</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -14035,10 +14023,10 @@
         </is>
       </c>
       <c r="B413" t="n">
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="C413" t="n">
-        <v>90.7636</v>
+        <v>75.49850426107911</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -14064,14 +14052,14 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>SVN</t>
         </is>
       </c>
       <c r="B414" t="n">
-        <v>2010</v>
+        <v>2017</v>
       </c>
       <c r="C414" t="n">
-        <v>68.81999999999999</v>
+        <v>78.88542635547751</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -14097,14 +14085,14 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>SVN</t>
         </is>
       </c>
       <c r="B415" t="n">
-        <v>2011</v>
+        <v>2018</v>
       </c>
       <c r="C415" t="n">
-        <v>70.48999999999999</v>
+        <v>79.74997659565619</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -14130,14 +14118,14 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>SVN</t>
         </is>
       </c>
       <c r="B416" t="n">
-        <v>2012</v>
+        <v>2019</v>
       </c>
       <c r="C416" t="n">
-        <v>73.43000000000001</v>
+        <v>83.1083578026717</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -14163,14 +14151,14 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>SVN</t>
         </is>
       </c>
       <c r="B417" t="n">
-        <v>2013</v>
+        <v>2020</v>
       </c>
       <c r="C417" t="n">
-        <v>74.1104</v>
+        <v>86.60130109000001</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -14196,14 +14184,14 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>SVN</t>
         </is>
       </c>
       <c r="B418" t="n">
-        <v>2014</v>
+        <v>2021</v>
       </c>
       <c r="C418" t="n">
-        <v>74.2317</v>
+        <v>89.00399523999999</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -14229,14 +14217,14 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>SVN</t>
         </is>
       </c>
       <c r="B419" t="n">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="C419" t="n">
-        <v>75.6688</v>
+        <v>88.91248552</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -14262,14 +14250,14 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>SVN</t>
         </is>
       </c>
       <c r="B420" t="n">
-        <v>2016</v>
+        <v>2023</v>
       </c>
       <c r="C420" t="n">
-        <v>76.4812</v>
+        <v>90.37794678</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -14295,14 +14283,14 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>SVN</t>
         </is>
       </c>
       <c r="B421" t="n">
-        <v>2017</v>
+        <v>2024</v>
       </c>
       <c r="C421" t="n">
-        <v>78.7192</v>
+        <v>90.76355486999999</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -14332,10 +14320,10 @@
         </is>
       </c>
       <c r="B422" t="n">
-        <v>2018</v>
+        <v>2010</v>
       </c>
       <c r="C422" t="n">
-        <v>80.68819999999999</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -14365,10 +14353,10 @@
         </is>
       </c>
       <c r="B423" t="n">
-        <v>2019</v>
+        <v>2011</v>
       </c>
       <c r="C423" t="n">
-        <v>80.8669</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -14398,10 +14386,10 @@
         </is>
       </c>
       <c r="B424" t="n">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="C424" t="n">
-        <v>81.3389</v>
+        <v>73.4300078241036</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -14431,10 +14419,10 @@
         </is>
       </c>
       <c r="B425" t="n">
-        <v>2021</v>
+        <v>2013</v>
       </c>
       <c r="C425" t="n">
-        <v>82.67059999999999</v>
+        <v>74.1104</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -14464,10 +14452,10 @@
         </is>
       </c>
       <c r="B426" t="n">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="C426" t="n">
-        <v>84.5401</v>
+        <v>74.2317116367383</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -14497,10 +14485,10 @@
         </is>
       </c>
       <c r="B427" t="n">
-        <v>2023</v>
+        <v>2015</v>
       </c>
       <c r="C427" t="n">
-        <v>85.994</v>
+        <v>75.66883869927899</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -14530,10 +14518,10 @@
         </is>
       </c>
       <c r="B428" t="n">
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="C428" t="n">
-        <v>87.6878</v>
+        <v>76.48119869518381</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -14559,14 +14547,14 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>UKR</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="B429" t="n">
-        <v>2010</v>
+        <v>2017</v>
       </c>
       <c r="C429" t="n">
-        <v>23.3</v>
+        <v>78.7191728513432</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -14592,14 +14580,14 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>UKR</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="B430" t="n">
-        <v>2011</v>
+        <v>2018</v>
       </c>
       <c r="C430" t="n">
-        <v>28.7083</v>
+        <v>80.6881675434288</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -14625,14 +14613,14 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>UKR</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="B431" t="n">
-        <v>2012</v>
+        <v>2019</v>
       </c>
       <c r="C431" t="n">
-        <v>35.27</v>
+        <v>80.8669444139622</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -14658,14 +14646,14 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>UKR</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="B432" t="n">
-        <v>2013</v>
+        <v>2020</v>
       </c>
       <c r="C432" t="n">
-        <v>40.9541</v>
+        <v>81.33889705</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -14691,14 +14679,14 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>UKR</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="B433" t="n">
-        <v>2014</v>
+        <v>2021</v>
       </c>
       <c r="C433" t="n">
-        <v>46.236</v>
+        <v>82.67062427</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -14724,14 +14712,14 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>UKR</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="B434" t="n">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="C434" t="n">
-        <v>48.8846</v>
+        <v>84.54009378000001</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -14757,14 +14745,14 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>UKR</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="B435" t="n">
-        <v>2016</v>
+        <v>2023</v>
       </c>
       <c r="C435" t="n">
-        <v>53.001</v>
+        <v>85.99404817999999</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -14790,14 +14778,14 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>UKR</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="B436" t="n">
-        <v>2017</v>
+        <v>2024</v>
       </c>
       <c r="C436" t="n">
-        <v>58.8895</v>
+        <v>87.68776013999999</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -14827,10 +14815,10 @@
         </is>
       </c>
       <c r="B437" t="n">
-        <v>2018</v>
+        <v>2010</v>
       </c>
       <c r="C437" t="n">
-        <v>62.5532</v>
+        <v>23.3</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -14860,10 +14848,10 @@
         </is>
       </c>
       <c r="B438" t="n">
-        <v>2019</v>
+        <v>2011</v>
       </c>
       <c r="C438" t="n">
-        <v>70.12479999999999</v>
+        <v>28.7082628400713</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -14893,10 +14881,10 @@
         </is>
       </c>
       <c r="B439" t="n">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="C439" t="n">
-        <v>75.03789999999999</v>
+        <v>35.27</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -14926,10 +14914,10 @@
         </is>
       </c>
       <c r="B440" t="n">
-        <v>2021</v>
+        <v>2013</v>
       </c>
       <c r="C440" t="n">
-        <v>79.2183</v>
+        <v>40.954128997</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -14959,10 +14947,10 @@
         </is>
       </c>
       <c r="B441" t="n">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="C441" t="n">
-        <v>82.67529999999999</v>
+        <v>46.2359754571651</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -14992,10 +14980,10 @@
         </is>
       </c>
       <c r="B442" t="n">
-        <v>2023</v>
+        <v>2015</v>
       </c>
       <c r="C442" t="n">
-        <v>82.3755</v>
+        <v>48.8846436813218</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -15021,14 +15009,14 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>MDA</t>
+          <t>UKR</t>
         </is>
       </c>
       <c r="B443" t="n">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C443" t="n">
-        <v>29.68</v>
+        <v>53.0009695981884</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -15054,14 +15042,14 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>MDA</t>
+          <t>UKR</t>
         </is>
       </c>
       <c r="B444" t="n">
-        <v>2011</v>
+        <v>2017</v>
       </c>
       <c r="C444" t="n">
-        <v>32.07</v>
+        <v>58.8894794459775</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -15087,14 +15075,14 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>MDA</t>
+          <t>UKR</t>
         </is>
       </c>
       <c r="B445" t="n">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="C445" t="n">
-        <v>34.65</v>
+        <v>62.5531553933869</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -15120,14 +15108,14 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>MDA</t>
+          <t>UKR</t>
         </is>
       </c>
       <c r="B446" t="n">
-        <v>2013</v>
+        <v>2019</v>
       </c>
       <c r="C446" t="n">
-        <v>37.44</v>
+        <v>70.1248442995263</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -15153,14 +15141,14 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>MDA</t>
+          <t>UKR</t>
         </is>
       </c>
       <c r="B447" t="n">
-        <v>2014</v>
+        <v>2020</v>
       </c>
       <c r="C447" t="n">
-        <v>67</v>
+        <v>75.03790911999999</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -15186,14 +15174,14 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>MDA</t>
+          <t>UKR</t>
         </is>
       </c>
       <c r="B448" t="n">
-        <v>2015</v>
+        <v>2021</v>
       </c>
       <c r="C448" t="n">
-        <v>69</v>
+        <v>79.21829353</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -15219,14 +15207,14 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>MDA</t>
+          <t>UKR</t>
         </is>
       </c>
       <c r="B449" t="n">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="C449" t="n">
-        <v>71</v>
+        <v>80.47429657000001</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -15252,14 +15240,14 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>MDA</t>
+          <t>UKR</t>
         </is>
       </c>
       <c r="B450" t="n">
-        <v>2017</v>
+        <v>2023</v>
       </c>
       <c r="C450" t="n">
-        <v>49.9</v>
+        <v>81.58059692</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -15285,14 +15273,14 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>MDA</t>
+          <t>UKR</t>
         </is>
       </c>
       <c r="B451" t="n">
-        <v>2018</v>
+        <v>2024</v>
       </c>
       <c r="C451" t="n">
-        <v>50.3</v>
+        <v>82.47489929</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -15322,10 +15310,10 @@
         </is>
       </c>
       <c r="B452" t="n">
-        <v>2019</v>
+        <v>2010</v>
       </c>
       <c r="C452" t="n">
-        <v>57.7605</v>
+        <v>29.68000031</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -15355,10 +15343,10 @@
         </is>
       </c>
       <c r="B453" t="n">
-        <v>2020</v>
+        <v>2011</v>
       </c>
       <c r="C453" t="n">
-        <v>58.2153</v>
+        <v>32.06999969</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -15388,10 +15376,10 @@
         </is>
       </c>
       <c r="B454" t="n">
-        <v>2021</v>
+        <v>2012</v>
       </c>
       <c r="C454" t="n">
-        <v>74.495</v>
+        <v>34.65000153</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -15421,10 +15409,10 @@
         </is>
       </c>
       <c r="B455" t="n">
-        <v>2022</v>
+        <v>2013</v>
       </c>
       <c r="C455" t="n">
-        <v>76.74120000000001</v>
+        <v>37.43999863</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -15454,10 +15442,10 @@
         </is>
       </c>
       <c r="B456" t="n">
-        <v>2023</v>
+        <v>2014</v>
       </c>
       <c r="C456" t="n">
-        <v>80.21259999999999</v>
+        <v>66.9999982002077</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -15483,14 +15471,14 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>GEO</t>
+          <t>MDA</t>
         </is>
       </c>
       <c r="B457" t="n">
-        <v>2010</v>
+        <v>2015</v>
       </c>
       <c r="C457" t="n">
-        <v>26.9</v>
+        <v>69.0000044661932</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -15516,14 +15504,14 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>GEO</t>
+          <t>MDA</t>
         </is>
       </c>
       <c r="B458" t="n">
-        <v>2011</v>
+        <v>2016</v>
       </c>
       <c r="C458" t="n">
-        <v>31.52</v>
+        <v>70.9999991066624</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -15549,14 +15537,14 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>GEO</t>
+          <t>MDA</t>
         </is>
       </c>
       <c r="B459" t="n">
-        <v>2012</v>
+        <v>2017</v>
       </c>
       <c r="C459" t="n">
-        <v>36.94</v>
+        <v>71.76709747</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -15582,14 +15570,14 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>GEO</t>
+          <t>MDA</t>
         </is>
       </c>
       <c r="B460" t="n">
-        <v>2013</v>
+        <v>2018</v>
       </c>
       <c r="C460" t="n">
-        <v>43.3</v>
+        <v>72.54239655000001</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -15615,14 +15603,14 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>GEO</t>
+          <t>MDA</t>
         </is>
       </c>
       <c r="B461" t="n">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="C461" t="n">
-        <v>49.1025</v>
+        <v>73.32610321</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -15648,14 +15636,14 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>GEO</t>
+          <t>MDA</t>
         </is>
       </c>
       <c r="B462" t="n">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="C462" t="n">
-        <v>47.5698</v>
+        <v>74.11830139</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -15681,14 +15669,14 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>GEO</t>
+          <t>MDA</t>
         </is>
       </c>
       <c r="B463" t="n">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="C463" t="n">
-        <v>58.4593</v>
+        <v>74.91899872</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -15714,14 +15702,14 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>GEO</t>
+          <t>MDA</t>
         </is>
       </c>
       <c r="B464" t="n">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="C464" t="n">
-        <v>59.7055</v>
+        <v>74.91899872</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -15747,14 +15735,14 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>GEO</t>
+          <t>MDA</t>
         </is>
       </c>
       <c r="B465" t="n">
-        <v>2018</v>
+        <v>2023</v>
       </c>
       <c r="C465" t="n">
-        <v>62.7179</v>
+        <v>76.50330353</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -15780,14 +15768,14 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>GEO</t>
+          <t>MDA</t>
         </is>
       </c>
       <c r="B466" t="n">
-        <v>2019</v>
+        <v>2024</v>
       </c>
       <c r="C466" t="n">
-        <v>68.8467</v>
+        <v>77.3687973</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -15817,10 +15805,10 @@
         </is>
       </c>
       <c r="B467" t="n">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="C467" t="n">
-        <v>72.5316</v>
+        <v>26.9</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -15850,10 +15838,10 @@
         </is>
       </c>
       <c r="B468" t="n">
-        <v>2021</v>
+        <v>2011</v>
       </c>
       <c r="C468" t="n">
-        <v>76.4427</v>
+        <v>31.52000046</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -15883,10 +15871,10 @@
         </is>
       </c>
       <c r="B469" t="n">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="C469" t="n">
-        <v>78.71129999999999</v>
+        <v>36.93999863</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -15916,10 +15904,10 @@
         </is>
       </c>
       <c r="B470" t="n">
-        <v>2023</v>
+        <v>2013</v>
       </c>
       <c r="C470" t="n">
-        <v>81.8843</v>
+        <v>43.3</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -15945,14 +15933,14 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>GEO</t>
         </is>
       </c>
       <c r="B471" t="n">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="C471" t="n">
-        <v>75.70999999999999</v>
+        <v>49.1024547144647</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -15978,14 +15966,14 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>GEO</t>
         </is>
       </c>
       <c r="B472" t="n">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="C472" t="n">
-        <v>74.44</v>
+        <v>47.5697596438736</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -16011,14 +15999,14 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>GEO</t>
         </is>
       </c>
       <c r="B473" t="n">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C473" t="n">
-        <v>76.70999999999999</v>
+        <v>58.4592896118725</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -16044,14 +16032,14 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>GEO</t>
         </is>
       </c>
       <c r="B474" t="n">
-        <v>2013</v>
+        <v>2017</v>
       </c>
       <c r="C474" t="n">
-        <v>77.8826</v>
+        <v>59.7055045962571</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -16077,14 +16065,14 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>GEO</t>
         </is>
       </c>
       <c r="B475" t="n">
-        <v>2014</v>
+        <v>2018</v>
       </c>
       <c r="C475" t="n">
-        <v>79.9843</v>
+        <v>62.7179081974285</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -16110,14 +16098,14 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>GEO</t>
         </is>
       </c>
       <c r="B476" t="n">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="C476" t="n">
-        <v>77.6347</v>
+        <v>68.8467135616978</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -16143,14 +16131,14 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>GEO</t>
         </is>
       </c>
       <c r="B477" t="n">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="C477" t="n">
-        <v>80.4759</v>
+        <v>72.53157487</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -16176,14 +16164,14 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>GEO</t>
         </is>
       </c>
       <c r="B478" t="n">
-        <v>2017</v>
+        <v>2021</v>
       </c>
       <c r="C478" t="n">
-        <v>81.62569999999999</v>
+        <v>76.4427093</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -16209,14 +16197,14 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>GEO</t>
         </is>
       </c>
       <c r="B479" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="C479" t="n">
-        <v>80.44889999999999</v>
+        <v>78.71127536</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -16242,14 +16230,14 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>GEO</t>
         </is>
       </c>
       <c r="B480" t="n">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="C480" t="n">
-        <v>82.8537</v>
+        <v>81.88425624</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -16275,14 +16263,14 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>GEO</t>
         </is>
       </c>
       <c r="B481" t="n">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="C481" t="n">
-        <v>89.9209</v>
+        <v>83.79855689</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -16312,10 +16300,10 @@
         </is>
       </c>
       <c r="B482" t="n">
-        <v>2021</v>
+        <v>2010</v>
       </c>
       <c r="C482" t="n">
-        <v>88.9256</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -16345,10 +16333,10 @@
         </is>
       </c>
       <c r="B483" t="n">
-        <v>2022</v>
+        <v>2011</v>
       </c>
       <c r="C483" t="n">
-        <v>89.0677</v>
+        <v>74.4399971746757</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -16378,10 +16366,10 @@
         </is>
       </c>
       <c r="B484" t="n">
-        <v>2023</v>
+        <v>2012</v>
       </c>
       <c r="C484" t="n">
-        <v>87.2131</v>
+        <v>76.7099901181121</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -16411,27 +16399,390 @@
         </is>
       </c>
       <c r="B485" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C485" t="n">
+        <v>77.8826</v>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>i99H</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>internet_users_pct</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>ITU API</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>SVK</t>
+        </is>
+      </c>
+      <c r="B486" t="n">
+        <v>2014</v>
+      </c>
+      <c r="C486" t="n">
+        <v>79.9843017656729</v>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>i99H</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>internet_users_pct</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>ITU API</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>SVK</t>
+        </is>
+      </c>
+      <c r="B487" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C487" t="n">
+        <v>77.6346820339875</v>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>i99H</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>internet_users_pct</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>ITU API</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>SVK</t>
+        </is>
+      </c>
+      <c r="B488" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C488" t="n">
+        <v>80.47585727566801</v>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>i99H</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>internet_users_pct</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>ITU API</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>SVK</t>
+        </is>
+      </c>
+      <c r="B489" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C489" t="n">
+        <v>81.6256675172655</v>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>i99H</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>internet_users_pct</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>ITU API</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>SVK</t>
+        </is>
+      </c>
+      <c r="B490" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C490" t="n">
+        <v>80.4489224826099</v>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>i99H</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>internet_users_pct</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>ITU API</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>SVK</t>
+        </is>
+      </c>
+      <c r="B491" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C491" t="n">
+        <v>82.8536605021784</v>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>i99H</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>internet_users_pct</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>ITU API</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>SVK</t>
+        </is>
+      </c>
+      <c r="B492" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C492" t="n">
+        <v>89.92090413</v>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>i99H</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>internet_users_pct</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>ITU API</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>SVK</t>
+        </is>
+      </c>
+      <c r="B493" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C493" t="n">
+        <v>88.92560523</v>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>i99H</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>internet_users_pct</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>ITU API</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>SVK</t>
+        </is>
+      </c>
+      <c r="B494" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C494" t="n">
+        <v>89.06766196</v>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>i99H</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>internet_users_pct</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>ITU API</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>SVK</t>
+        </is>
+      </c>
+      <c r="B495" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C495" t="n">
+        <v>87.21313429999999</v>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>i99H</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>internet_users_pct</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>ITU API</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>SVK</t>
+        </is>
+      </c>
+      <c r="B496" t="n">
         <v>2024</v>
       </c>
-      <c r="C485" t="n">
-        <v>89.82510000000001</v>
-      </c>
-      <c r="D485" t="inlineStr">
-        <is>
-          <t>i99H</t>
-        </is>
-      </c>
-      <c r="E485" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="F485" t="inlineStr">
-        <is>
-          <t>internet_users_pct</t>
-        </is>
-      </c>
-      <c r="G485" t="inlineStr">
+      <c r="C496" t="n">
+        <v>89.82507031999999</v>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>i99H</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>internet_users_pct</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
         <is>
           <t>ITU API</t>
         </is>
